--- a/audit/cis_reports/192.168.1.5_cis_benchmark.xlsx
+++ b/audit/cis_reports/192.168.1.5_cis_benchmark.xlsx
@@ -22,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="15">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -105,6 +105,12 @@
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="007A5800"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="009C2B26"/>
       <sz val="10"/>
     </font>
     <font>
@@ -197,7 +203,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -247,10 +253,13 @@
     <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
@@ -867,7 +876,7 @@
     <row r="4" ht="16" customHeight="1">
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Host: Docker-2204-DA-AUTO   |   OS: Ubuntu 22.04   |   Generated: 2026-05-11T01:58:04Z</t>
+          <t>Host: Docker-2204-DA-AUTO   |   OS: Ubuntu 22.04   |   Generated: 2026-05-11T10:07:21Z</t>
         </is>
       </c>
     </row>
@@ -902,7 +911,7 @@
         <v>14</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" s="7" t="n">
         <v>5</v>
@@ -1382,9 +1391,9 @@
           <t>Ensure that the version of Docker is up to date</t>
         </is>
       </c>
-      <c r="I33" s="16" t="inlineStr">
-        <is>
-          <t>TRUE</t>
+      <c r="I33" s="17" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="J33" s="12" t="inlineStr">
@@ -2070,9 +2079,9 @@
           <t>Ensure that the version of Docker is up to date</t>
         </is>
       </c>
-      <c r="E21" s="16" t="inlineStr">
-        <is>
-          <t>TRUE</t>
+      <c r="E21" s="17" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="F21" s="12" t="inlineStr">
@@ -2101,1078 +2110,1078 @@
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
-      <c r="B1" s="17" t="inlineStr">
+      <c r="B1" s="18" t="inlineStr">
         <is>
           <t>Raw JSON Output (audit_data.json)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="14" customHeight="1">
-      <c r="B2" s="18" t="inlineStr">
+      <c r="B2" s="19" t="inlineStr">
         <is>
           <t>{</t>
         </is>
       </c>
     </row>
     <row r="3" ht="14" customHeight="1">
-      <c r="B3" s="18" t="inlineStr">
+      <c r="B3" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">  "meta": {</t>
         </is>
       </c>
     </row>
     <row r="4" ht="14" customHeight="1">
-      <c r="B4" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    "fail": 0,</t>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    "fail": 1,</t>
         </is>
       </c>
     </row>
     <row r="5" ht="14" customHeight="1">
-      <c r="B5" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    "generated": "2026-05-11T01:58:04Z",</t>
+      <c r="B5" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    "generated": "2026-05-11T10:07:21Z",</t>
         </is>
       </c>
     </row>
     <row r="6" ht="14" customHeight="1">
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B6" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">    "host": "Docker-2204-DA-AUTO",</t>
         </is>
       </c>
     </row>
     <row r="7" ht="14" customHeight="1">
-      <c r="B7" s="18" t="inlineStr">
+      <c r="B7" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">    "info": 5,</t>
         </is>
       </c>
     </row>
     <row r="8" ht="14" customHeight="1">
-      <c r="B8" s="18" t="inlineStr">
+      <c r="B8" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">    "os": "Ubuntu 22.04",</t>
         </is>
       </c>
     </row>
     <row r="9" ht="14" customHeight="1">
-      <c r="B9" s="18" t="inlineStr">
+      <c r="B9" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">    "pass": 14,</t>
         </is>
       </c>
     </row>
     <row r="10" ht="14" customHeight="1">
-      <c r="B10" s="18" t="inlineStr">
+      <c r="B10" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">    "total": 20</t>
         </is>
       </c>
     </row>
     <row r="11" ht="14" customHeight="1">
-      <c r="B11" s="18" t="inlineStr">
+      <c r="B11" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">  },</t>
         </is>
       </c>
     </row>
     <row r="12" ht="14" customHeight="1">
-      <c r="B12" s="18" t="inlineStr">
+      <c r="B12" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">  "results": [</t>
         </is>
       </c>
     </row>
     <row r="13" ht="14" customHeight="1">
-      <c r="B13" s="18" t="inlineStr">
+      <c r="B13" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">    {</t>
         </is>
       </c>
     </row>
     <row r="14" ht="14" customHeight="1">
-      <c r="B14" s="18" t="inlineStr">
+      <c r="B14" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">      "details": "[PASS] 1.1.1 - Separate mount point created",</t>
         </is>
       </c>
     </row>
     <row r="15" ht="14" customHeight="1">
-      <c r="B15" s="18" t="inlineStr">
+      <c r="B15" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">      "id": "1.1.1",</t>
         </is>
       </c>
     </row>
     <row r="16" ht="14" customHeight="1">
-      <c r="B16" s="18" t="inlineStr">
+      <c r="B16" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">      "section": "1.1 Host Configuration",</t>
         </is>
       </c>
     </row>
     <row r="17" ht="14" customHeight="1">
-      <c r="B17" s="18" t="inlineStr">
+      <c r="B17" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">      "status": "PASS",</t>
         </is>
       </c>
     </row>
     <row r="18" ht="14" customHeight="1">
-      <c r="B18" s="18" t="inlineStr">
+      <c r="B18" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">      "title": "Ensure a separate partition for containers has been created"</t>
         </is>
       </c>
     </row>
     <row r="19" ht="14" customHeight="1">
-      <c r="B19" s="18" t="inlineStr">
+      <c r="B19" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">    },</t>
         </is>
       </c>
     </row>
     <row r="20" ht="14" customHeight="1">
-      <c r="B20" s="18" t="inlineStr">
+      <c r="B20" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">    {</t>
         </is>
       </c>
     </row>
     <row r="21" ht="14" customHeight="1">
-      <c r="B21" s="18" t="inlineStr">
+      <c r="B21" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">      "details": "[INFO] 1.1.2 - Manual review required. Docker group members: docker:x:999:",</t>
         </is>
       </c>
     </row>
     <row r="22" ht="14" customHeight="1">
-      <c r="B22" s="18" t="inlineStr">
+      <c r="B22" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">      "id": "1.1.2",</t>
         </is>
       </c>
     </row>
     <row r="23" ht="14" customHeight="1">
-      <c r="B23" s="18" t="inlineStr">
+      <c r="B23" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">      "section": "1.1 Host Configuration",</t>
         </is>
       </c>
     </row>
     <row r="24" ht="14" customHeight="1">
-      <c r="B24" s="18" t="inlineStr">
+      <c r="B24" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">      "status": "INFO",</t>
         </is>
       </c>
     </row>
     <row r="25" ht="14" customHeight="1">
-      <c r="B25" s="18" t="inlineStr">
+      <c r="B25" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">      "title": "Ensure only trusted users are allowed to control Docker daemon"</t>
         </is>
       </c>
     </row>
     <row r="26" ht="14" customHeight="1">
-      <c r="B26" s="18" t="inlineStr">
+      <c r="B26" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">    },</t>
         </is>
       </c>
     </row>
     <row r="27" ht="14" customHeight="1">
-      <c r="B27" s="18" t="inlineStr">
+      <c r="B27" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">    {</t>
         </is>
       </c>
     </row>
     <row r="28" ht="14" customHeight="1">
-      <c r="B28" s="18" t="inlineStr">
+      <c r="B28" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">      "details": "[PASS] 1.1.3 - Auditing is configured for the Docker daemon",</t>
         </is>
       </c>
     </row>
     <row r="29" ht="14" customHeight="1">
-      <c r="B29" s="18" t="inlineStr">
+      <c r="B29" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">      "id": "1.1.3",</t>
         </is>
       </c>
     </row>
     <row r="30" ht="14" customHeight="1">
-      <c r="B30" s="18" t="inlineStr">
+      <c r="B30" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">      "section": "1.1 Host Configuration",</t>
         </is>
       </c>
     </row>
     <row r="31" ht="14" customHeight="1">
-      <c r="B31" s="18" t="inlineStr">
+      <c r="B31" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">      "status": "PASS",</t>
         </is>
       </c>
     </row>
     <row r="32" ht="14" customHeight="1">
-      <c r="B32" s="18" t="inlineStr">
+      <c r="B32" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">      "title": "Ensure auditing is configured for the Docker daemon"</t>
         </is>
       </c>
     </row>
     <row r="33" ht="14" customHeight="1">
-      <c r="B33" s="18" t="inlineStr">
+      <c r="B33" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">    },</t>
         </is>
       </c>
     </row>
     <row r="34" ht="14" customHeight="1">
-      <c r="B34" s="18" t="inlineStr">
+      <c r="B34" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">    {</t>
         </is>
       </c>
     </row>
     <row r="35" ht="14" customHeight="1">
-      <c r="B35" s="18" t="inlineStr">
+      <c r="B35" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">      "details": "[PASS] 1.1.4 - Auditing is configured for /run/containerd",</t>
         </is>
       </c>
     </row>
     <row r="36" ht="14" customHeight="1">
-      <c r="B36" s="18" t="inlineStr">
+      <c r="B36" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">      "id": "1.1.4",</t>
         </is>
       </c>
     </row>
     <row r="37" ht="14" customHeight="1">
-      <c r="B37" s="18" t="inlineStr">
+      <c r="B37" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">      "section": "1.1 Host Configuration",</t>
         </is>
       </c>
     </row>
     <row r="38" ht="14" customHeight="1">
-      <c r="B38" s="18" t="inlineStr">
+      <c r="B38" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">      "status": "PASS",</t>
         </is>
       </c>
     </row>
     <row r="39" ht="14" customHeight="1">
-      <c r="B39" s="18" t="inlineStr">
+      <c r="B39" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">      "title": "Ensure auditing is configured for Docker files and directories /run/containerd"</t>
         </is>
       </c>
     </row>
     <row r="40" ht="14" customHeight="1">
-      <c r="B40" s="18" t="inlineStr">
+      <c r="B40" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">    },</t>
         </is>
       </c>
     </row>
     <row r="41" ht="14" customHeight="1">
-      <c r="B41" s="18" t="inlineStr">
+      <c r="B41" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">    {</t>
         </is>
       </c>
     </row>
     <row r="42" ht="14" customHeight="1">
-      <c r="B42" s="18" t="inlineStr">
+      <c r="B42" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">      "details": "[PASS] 1.1.5 - Auditing is configured for /var/lib/docker",</t>
         </is>
       </c>
     </row>
     <row r="43" ht="14" customHeight="1">
-      <c r="B43" s="18" t="inlineStr">
+      <c r="B43" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">      "id": "1.1.5",</t>
         </is>
       </c>
     </row>
     <row r="44" ht="14" customHeight="1">
-      <c r="B44" s="18" t="inlineStr">
+      <c r="B44" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">      "section": "1.1 Host Configuration",</t>
         </is>
       </c>
     </row>
     <row r="45" ht="14" customHeight="1">
-      <c r="B45" s="18" t="inlineStr">
+      <c r="B45" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">      "status": "PASS",</t>
         </is>
       </c>
     </row>
     <row r="46" ht="14" customHeight="1">
-      <c r="B46" s="18" t="inlineStr">
+      <c r="B46" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">      "title": "Ensure auditing is configured for Docker files and directories /var/lib/docker"</t>
         </is>
       </c>
     </row>
     <row r="47" ht="14" customHeight="1">
-      <c r="B47" s="18" t="inlineStr">
+      <c r="B47" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">    },</t>
         </is>
       </c>
     </row>
     <row r="48" ht="14" customHeight="1">
-      <c r="B48" s="18" t="inlineStr">
+      <c r="B48" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">    {</t>
         </is>
       </c>
     </row>
     <row r="49" ht="14" customHeight="1">
-      <c r="B49" s="18" t="inlineStr">
+      <c r="B49" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">      "details": "[PASS] 1.1.6 - Auditing is configured for /etc/docker",</t>
         </is>
       </c>
     </row>
     <row r="50" ht="14" customHeight="1">
-      <c r="B50" s="18" t="inlineStr">
+      <c r="B50" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">      "id": "1.1.6",</t>
         </is>
       </c>
     </row>
     <row r="51" ht="14" customHeight="1">
-      <c r="B51" s="18" t="inlineStr">
+      <c r="B51" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">      "section": "1.1 Host Configuration",</t>
         </is>
       </c>
     </row>
     <row r="52" ht="14" customHeight="1">
-      <c r="B52" s="18" t="inlineStr">
+      <c r="B52" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">      "status": "PASS",</t>
         </is>
       </c>
     </row>
     <row r="53" ht="14" customHeight="1">
-      <c r="B53" s="18" t="inlineStr">
+      <c r="B53" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">      "title": "Ensure auditing is configured for Docker files and directories /etc/docker"</t>
         </is>
       </c>
     </row>
     <row r="54" ht="14" customHeight="1">
-      <c r="B54" s="18" t="inlineStr">
+      <c r="B54" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">    },</t>
         </is>
       </c>
     </row>
     <row r="55" ht="14" customHeight="1">
-      <c r="B55" s="18" t="inlineStr">
+      <c r="B55" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">    {</t>
         </is>
       </c>
     </row>
     <row r="56" ht="14" customHeight="1">
-      <c r="B56" s="18" t="inlineStr">
+      <c r="B56" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">      "details": "[PASS] 1.1.7 - Auditing is configured for docker.service",</t>
         </is>
       </c>
     </row>
     <row r="57" ht="14" customHeight="1">
-      <c r="B57" s="18" t="inlineStr">
+      <c r="B57" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">      "id": "1.1.7",</t>
         </is>
       </c>
     </row>
     <row r="58" ht="14" customHeight="1">
-      <c r="B58" s="18" t="inlineStr">
+      <c r="B58" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">      "section": "1.1 Host Configuration",</t>
         </is>
       </c>
     </row>
     <row r="59" ht="14" customHeight="1">
-      <c r="B59" s="18" t="inlineStr">
+      <c r="B59" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">      "status": "PASS",</t>
         </is>
       </c>
     </row>
     <row r="60" ht="14" customHeight="1">
-      <c r="B60" s="18" t="inlineStr">
+      <c r="B60" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">      "title": "Ensure auditing is configured for Docker files and directories docker.service"</t>
         </is>
       </c>
     </row>
     <row r="61" ht="14" customHeight="1">
-      <c r="B61" s="18" t="inlineStr">
+      <c r="B61" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">    },</t>
         </is>
       </c>
     </row>
     <row r="62" ht="14" customHeight="1">
-      <c r="B62" s="18" t="inlineStr">
+      <c r="B62" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">    {</t>
         </is>
       </c>
     </row>
     <row r="63" ht="14" customHeight="1">
-      <c r="B63" s="18" t="inlineStr">
+      <c r="B63" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">      "details": "[PASS] 1.1.8 - Auditing is configured for containerd.sock",</t>
         </is>
       </c>
     </row>
     <row r="64" ht="14" customHeight="1">
-      <c r="B64" s="18" t="inlineStr">
+      <c r="B64" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">      "id": "1.1.8",</t>
         </is>
       </c>
     </row>
     <row r="65" ht="14" customHeight="1">
-      <c r="B65" s="18" t="inlineStr">
+      <c r="B65" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">      "section": "1.1 Host Configuration",</t>
         </is>
       </c>
     </row>
     <row r="66" ht="14" customHeight="1">
-      <c r="B66" s="18" t="inlineStr">
+      <c r="B66" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">      "status": "PASS",</t>
         </is>
       </c>
     </row>
     <row r="67" ht="14" customHeight="1">
-      <c r="B67" s="18" t="inlineStr">
+      <c r="B67" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">      "title": "Ensure auditing is configured for Docker files and directories containerd.sock"</t>
         </is>
       </c>
     </row>
     <row r="68" ht="14" customHeight="1">
-      <c r="B68" s="18" t="inlineStr">
+      <c r="B68" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">    },</t>
         </is>
       </c>
     </row>
     <row r="69" ht="14" customHeight="1">
-      <c r="B69" s="18" t="inlineStr">
+      <c r="B69" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">    {</t>
         </is>
       </c>
     </row>
     <row r="70" ht="14" customHeight="1">
-      <c r="B70" s="18" t="inlineStr">
+      <c r="B70" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">      "details": "[PASS] 1.1.9 - Auditing is configured for the Docker socket",</t>
         </is>
       </c>
     </row>
     <row r="71" ht="14" customHeight="1">
-      <c r="B71" s="18" t="inlineStr">
+      <c r="B71" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">      "id": "1.1.9",</t>
         </is>
       </c>
     </row>
     <row r="72" ht="14" customHeight="1">
-      <c r="B72" s="18" t="inlineStr">
+      <c r="B72" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">      "section": "1.1 Host Configuration",</t>
         </is>
       </c>
     </row>
     <row r="73" ht="14" customHeight="1">
-      <c r="B73" s="18" t="inlineStr">
+      <c r="B73" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">      "status": "PASS",</t>
         </is>
       </c>
     </row>
     <row r="74" ht="14" customHeight="1">
-      <c r="B74" s="18" t="inlineStr">
+      <c r="B74" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">      "title": "Ensure auditing is configured for Docker files and directories - docker.socket"</t>
         </is>
       </c>
     </row>
     <row r="75" ht="14" customHeight="1">
-      <c r="B75" s="18" t="inlineStr">
+      <c r="B75" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">    },</t>
         </is>
       </c>
     </row>
     <row r="76" ht="14" customHeight="1">
-      <c r="B76" s="18" t="inlineStr">
+      <c r="B76" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">    {</t>
         </is>
       </c>
     </row>
     <row r="77" ht="14" customHeight="1">
-      <c r="B77" s="18" t="inlineStr">
+      <c r="B77" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">      "details": "[PASS] 1.1.10 - Auditing is configured for /etc/default/docker",</t>
         </is>
       </c>
     </row>
     <row r="78" ht="14" customHeight="1">
-      <c r="B78" s="18" t="inlineStr">
+      <c r="B78" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">      "id": "1.1.10",</t>
         </is>
       </c>
     </row>
     <row r="79" ht="14" customHeight="1">
-      <c r="B79" s="18" t="inlineStr">
+      <c r="B79" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">      "section": "1.1 Host Configuration",</t>
         </is>
       </c>
     </row>
     <row r="80" ht="14" customHeight="1">
-      <c r="B80" s="18" t="inlineStr">
+      <c r="B80" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">      "status": "PASS",</t>
         </is>
       </c>
     </row>
     <row r="81" ht="14" customHeight="1">
-      <c r="B81" s="18" t="inlineStr">
+      <c r="B81" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">      "title": "Ensure auditing is configured for Docker files and directories /etc/default/docker"</t>
         </is>
       </c>
     </row>
     <row r="82" ht="14" customHeight="1">
-      <c r="B82" s="18" t="inlineStr">
+      <c r="B82" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">    },</t>
         </is>
       </c>
     </row>
     <row r="83" ht="14" customHeight="1">
-      <c r="B83" s="18" t="inlineStr">
+      <c r="B83" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">    {</t>
         </is>
       </c>
     </row>
     <row r="84" ht="14" customHeight="1">
-      <c r="B84" s="18" t="inlineStr">
+      <c r="B84" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">      "details": "[PASS] 1.1.11 - Auditing is configured for /etc/docker/daemon.json",</t>
         </is>
       </c>
     </row>
     <row r="85" ht="14" customHeight="1">
-      <c r="B85" s="18" t="inlineStr">
+      <c r="B85" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">      "id": "1.1.11",</t>
         </is>
       </c>
     </row>
     <row r="86" ht="14" customHeight="1">
-      <c r="B86" s="18" t="inlineStr">
+      <c r="B86" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">      "section": "1.1 Host Configuration",</t>
         </is>
       </c>
     </row>
     <row r="87" ht="14" customHeight="1">
-      <c r="B87" s="18" t="inlineStr">
+      <c r="B87" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">      "status": "PASS",</t>
         </is>
       </c>
     </row>
     <row r="88" ht="14" customHeight="1">
-      <c r="B88" s="18" t="inlineStr">
+      <c r="B88" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">      "title": "Ensure auditing is configured for Docker files and directories /etc/docker/daemon.json"</t>
         </is>
       </c>
     </row>
     <row r="89" ht="14" customHeight="1">
-      <c r="B89" s="18" t="inlineStr">
+      <c r="B89" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">    },</t>
         </is>
       </c>
     </row>
     <row r="90" ht="14" customHeight="1">
-      <c r="B90" s="18" t="inlineStr">
+      <c r="B90" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">    {</t>
         </is>
       </c>
     </row>
     <row r="91" ht="14" customHeight="1">
-      <c r="B91" s="18" t="inlineStr">
+      <c r="B91" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">      "details": "[PASS] 1.1.12 - Auditing is configured for /etc/containerd/config.toml",</t>
         </is>
       </c>
     </row>
     <row r="92" ht="14" customHeight="1">
-      <c r="B92" s="18" t="inlineStr">
+      <c r="B92" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">      "id": "1.1.12",</t>
         </is>
       </c>
     </row>
     <row r="93" ht="14" customHeight="1">
-      <c r="B93" s="18" t="inlineStr">
+      <c r="B93" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">      "section": "1.1 Host Configuration",</t>
         </is>
       </c>
     </row>
     <row r="94" ht="14" customHeight="1">
-      <c r="B94" s="18" t="inlineStr">
+      <c r="B94" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">      "status": "PASS",</t>
         </is>
       </c>
     </row>
     <row r="95" ht="14" customHeight="1">
-      <c r="B95" s="18" t="inlineStr">
+      <c r="B95" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">      "title": "Ensure auditing is configured for Docker files and directories /etc/containerd/config.toml"</t>
         </is>
       </c>
     </row>
     <row r="96" ht="14" customHeight="1">
-      <c r="B96" s="18" t="inlineStr">
+      <c r="B96" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">    },</t>
         </is>
       </c>
     </row>
     <row r="97" ht="14" customHeight="1">
-      <c r="B97" s="18" t="inlineStr">
+      <c r="B97" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">    {</t>
         </is>
       </c>
     </row>
     <row r="98" ht="14" customHeight="1">
-      <c r="B98" s="18" t="inlineStr">
+      <c r="B98" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">      "details": "[INFO] 1.1.13 - /etc/sysconfig/docker does not exist",</t>
         </is>
       </c>
     </row>
     <row r="99" ht="14" customHeight="1">
-      <c r="B99" s="18" t="inlineStr">
+      <c r="B99" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">      "id": "1.1.13",</t>
         </is>
       </c>
     </row>
     <row r="100" ht="14" customHeight="1">
-      <c r="B100" s="18" t="inlineStr">
+      <c r="B100" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">      "section": "1.1 Host Configuration",</t>
         </is>
       </c>
     </row>
     <row r="101" ht="14" customHeight="1">
-      <c r="B101" s="18" t="inlineStr">
+      <c r="B101" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">      "status": "INFO",</t>
         </is>
       </c>
     </row>
     <row r="102" ht="14" customHeight="1">
-      <c r="B102" s="18" t="inlineStr">
+      <c r="B102" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">      "title": "Ensure auditing is configured for Docker files and directories /etc/sysconfig/docker"</t>
         </is>
       </c>
     </row>
     <row r="103" ht="14" customHeight="1">
-      <c r="B103" s="18" t="inlineStr">
+      <c r="B103" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">    },</t>
         </is>
       </c>
     </row>
     <row r="104" ht="14" customHeight="1">
-      <c r="B104" s="18" t="inlineStr">
+      <c r="B104" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">    {</t>
         </is>
       </c>
     </row>
     <row r="105" ht="14" customHeight="1">
-      <c r="B105" s="18" t="inlineStr">
+      <c r="B105" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">      "details": "[PASS] 1.1.14 - Auditing is configured for /usr/bin/containerd",</t>
         </is>
       </c>
     </row>
     <row r="106" ht="14" customHeight="1">
-      <c r="B106" s="18" t="inlineStr">
+      <c r="B106" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">      "id": "1.1.14",</t>
         </is>
       </c>
     </row>
     <row r="107" ht="14" customHeight="1">
-      <c r="B107" s="18" t="inlineStr">
+      <c r="B107" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">      "section": "1.1 Host Configuration",</t>
         </is>
       </c>
     </row>
     <row r="108" ht="14" customHeight="1">
-      <c r="B108" s="18" t="inlineStr">
+      <c r="B108" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">      "status": "PASS",</t>
         </is>
       </c>
     </row>
     <row r="109" ht="14" customHeight="1">
-      <c r="B109" s="18" t="inlineStr">
+      <c r="B109" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">      "title": "Ensure auditing is configured for Docker files and directories /usr/bin/containerd"</t>
         </is>
       </c>
     </row>
     <row r="110" ht="14" customHeight="1">
-      <c r="B110" s="18" t="inlineStr">
+      <c r="B110" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">    },</t>
         </is>
       </c>
     </row>
     <row r="111" ht="14" customHeight="1">
-      <c r="B111" s="18" t="inlineStr">
+      <c r="B111" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">    {</t>
         </is>
       </c>
     </row>
     <row r="112" ht="14" customHeight="1">
-      <c r="B112" s="18" t="inlineStr">
+      <c r="B112" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">      "details": "[INFO] 1.1.15 - /usr/bin/containerd-shim does not exist",</t>
         </is>
       </c>
     </row>
     <row r="113" ht="14" customHeight="1">
-      <c r="B113" s="18" t="inlineStr">
+      <c r="B113" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">      "id": "1.1.15",</t>
         </is>
       </c>
     </row>
     <row r="114" ht="14" customHeight="1">
-      <c r="B114" s="18" t="inlineStr">
+      <c r="B114" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">      "section": "1.1 Host Configuration",</t>
         </is>
       </c>
     </row>
     <row r="115" ht="14" customHeight="1">
-      <c r="B115" s="18" t="inlineStr">
+      <c r="B115" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">      "status": "INFO",</t>
         </is>
       </c>
     </row>
     <row r="116" ht="14" customHeight="1">
-      <c r="B116" s="18" t="inlineStr">
+      <c r="B116" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">      "title": "Ensure auditing is configured for Docker files and directories /usr/bin/containerd-shim"</t>
         </is>
       </c>
     </row>
     <row r="117" ht="14" customHeight="1">
-      <c r="B117" s="18" t="inlineStr">
+      <c r="B117" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">    },</t>
         </is>
       </c>
     </row>
     <row r="118" ht="14" customHeight="1">
-      <c r="B118" s="18" t="inlineStr">
+      <c r="B118" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">    {</t>
         </is>
       </c>
     </row>
     <row r="119" ht="14" customHeight="1">
-      <c r="B119" s="18" t="inlineStr">
+      <c r="B119" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">      "details": "[INFO] 1.1.16 - /usr/bin/containerd-shim-runc-v1 does not exist",</t>
         </is>
       </c>
     </row>
     <row r="120" ht="14" customHeight="1">
-      <c r="B120" s="18" t="inlineStr">
+      <c r="B120" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">      "id": "1.1.16",</t>
         </is>
       </c>
     </row>
     <row r="121" ht="14" customHeight="1">
-      <c r="B121" s="18" t="inlineStr">
+      <c r="B121" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">      "section": "1.1 Host Configuration",</t>
         </is>
       </c>
     </row>
     <row r="122" ht="14" customHeight="1">
-      <c r="B122" s="18" t="inlineStr">
+      <c r="B122" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">      "status": "INFO",</t>
         </is>
       </c>
     </row>
     <row r="123" ht="14" customHeight="1">
-      <c r="B123" s="18" t="inlineStr">
+      <c r="B123" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">      "title": "Ensure auditing is configured for Docker files and directories /usr/bin/containerd-shim-runc-v1"</t>
         </is>
       </c>
     </row>
     <row r="124" ht="14" customHeight="1">
-      <c r="B124" s="18" t="inlineStr">
+      <c r="B124" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">    },</t>
         </is>
       </c>
     </row>
     <row r="125" ht="14" customHeight="1">
-      <c r="B125" s="18" t="inlineStr">
+      <c r="B125" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">    {</t>
         </is>
       </c>
     </row>
     <row r="126" ht="14" customHeight="1">
-      <c r="B126" s="18" t="inlineStr">
+      <c r="B126" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">      "details": "[PASS] 1.1.17 - Auditing is configured for /usr/bin/containerd-shim-runc-v2",</t>
         </is>
       </c>
     </row>
     <row r="127" ht="14" customHeight="1">
-      <c r="B127" s="18" t="inlineStr">
+      <c r="B127" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">      "id": "1.1.17",</t>
         </is>
       </c>
     </row>
     <row r="128" ht="14" customHeight="1">
-      <c r="B128" s="18" t="inlineStr">
+      <c r="B128" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">      "section": "1.1 Host Configuration",</t>
         </is>
       </c>
     </row>
     <row r="129" ht="14" customHeight="1">
-      <c r="B129" s="18" t="inlineStr">
+      <c r="B129" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">      "status": "PASS",</t>
         </is>
       </c>
     </row>
     <row r="130" ht="14" customHeight="1">
-      <c r="B130" s="18" t="inlineStr">
+      <c r="B130" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">      "title": "Ensure auditing is configured for Docker files and directories /usr/bin/containerd-shim-runc-v2"</t>
         </is>
       </c>
     </row>
     <row r="131" ht="14" customHeight="1">
-      <c r="B131" s="18" t="inlineStr">
+      <c r="B131" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">    },</t>
         </is>
       </c>
     </row>
     <row r="132" ht="14" customHeight="1">
-      <c r="B132" s="18" t="inlineStr">
+      <c r="B132" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">    {</t>
         </is>
       </c>
     </row>
     <row r="133" ht="14" customHeight="1">
-      <c r="B133" s="18" t="inlineStr">
+      <c r="B133" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">      "details": "[PASS] 1.1.18 - Auditing is configured for /usr/bin/runc",</t>
         </is>
       </c>
     </row>
     <row r="134" ht="14" customHeight="1">
-      <c r="B134" s="18" t="inlineStr">
+      <c r="B134" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">      "id": "1.1.18",</t>
         </is>
       </c>
     </row>
     <row r="135" ht="14" customHeight="1">
-      <c r="B135" s="18" t="inlineStr">
+      <c r="B135" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">      "section": "1.1 Host Configuration",</t>
         </is>
       </c>
     </row>
     <row r="136" ht="14" customHeight="1">
-      <c r="B136" s="18" t="inlineStr">
+      <c r="B136" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">      "status": "PASS",</t>
         </is>
       </c>
     </row>
     <row r="137" ht="14" customHeight="1">
-      <c r="B137" s="18" t="inlineStr">
+      <c r="B137" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">      "title": "Ensure auditing is configured for Docker files and directories /usr/bin/runc"</t>
         </is>
       </c>
     </row>
     <row r="138" ht="14" customHeight="1">
-      <c r="B138" s="18" t="inlineStr">
+      <c r="B138" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">    },</t>
         </is>
       </c>
     </row>
     <row r="139" ht="14" customHeight="1">
-      <c r="B139" s="18" t="inlineStr">
+      <c r="B139" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">    {</t>
         </is>
       </c>
     </row>
     <row r="140" ht="14" customHeight="1">
-      <c r="B140" s="18" t="inlineStr">
+      <c r="B140" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">      "details": "[INFO] 1.2.1 - Manual review required: verify host hardening via CIS benchmark for the OS",</t>
         </is>
       </c>
     </row>
     <row r="141" ht="14" customHeight="1">
-      <c r="B141" s="18" t="inlineStr">
+      <c r="B141" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">      "id": "1.2.1",</t>
         </is>
       </c>
     </row>
     <row r="142" ht="14" customHeight="1">
-      <c r="B142" s="18" t="inlineStr">
+      <c r="B142" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">      "section": "1.2 Docker Installation",</t>
         </is>
       </c>
     </row>
     <row r="143" ht="14" customHeight="1">
-      <c r="B143" s="18" t="inlineStr">
+      <c r="B143" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">      "status": "INFO",</t>
         </is>
       </c>
     </row>
     <row r="144" ht="14" customHeight="1">
-      <c r="B144" s="18" t="inlineStr">
+      <c r="B144" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">      "title": "Ensure the container host has been Hardened"</t>
         </is>
       </c>
     </row>
     <row r="145" ht="14" customHeight="1">
-      <c r="B145" s="18" t="inlineStr">
+      <c r="B145" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">    },</t>
         </is>
       </c>
     </row>
     <row r="146" ht="14" customHeight="1">
-      <c r="B146" s="18" t="inlineStr">
+      <c r="B146" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">    {</t>
         </is>
       </c>
     </row>
     <row r="147" ht="14" customHeight="1">
-      <c r="B147" s="18" t="inlineStr">
+      <c r="B147" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">      "details": "[FAIL] 1.2.2 - Docker updates are available. Update to the latest version.",</t>
         </is>
       </c>
     </row>
     <row r="148" ht="14" customHeight="1">
-      <c r="B148" s="18" t="inlineStr">
+      <c r="B148" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">      "id": "1.2.2",</t>
         </is>
       </c>
     </row>
     <row r="149" ht="14" customHeight="1">
-      <c r="B149" s="18" t="inlineStr">
+      <c r="B149" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">      "section": "1.2 Docker Installation",</t>
         </is>
       </c>
     </row>
     <row r="150" ht="14" customHeight="1">
-      <c r="B150" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      "status": "TRUE",</t>
+      <c r="B150" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      "status": "FAIL",</t>
         </is>
       </c>
     </row>
     <row r="151" ht="14" customHeight="1">
-      <c r="B151" s="18" t="inlineStr">
+      <c r="B151" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">      "title": "Ensure that the version of Docker is up to date"</t>
         </is>
       </c>
     </row>
     <row r="152" ht="14" customHeight="1">
-      <c r="B152" s="18" t="inlineStr">
+      <c r="B152" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">    }</t>
         </is>
       </c>
     </row>
     <row r="153" ht="14" customHeight="1">
-      <c r="B153" s="18" t="inlineStr">
+      <c r="B153" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">  ]</t>
         </is>
       </c>
     </row>
     <row r="154" ht="14" customHeight="1">
-      <c r="B154" s="18" t="inlineStr">
+      <c r="B154" s="19" t="inlineStr">
         <is>
           <t>}</t>
         </is>
@@ -3227,7 +3236,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
